--- a/artfynd/A 2443-2023 artfynd.xlsx
+++ b/artfynd/A 2443-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121139133</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>8424</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2443-2023 artfynd.xlsx
+++ b/artfynd/A 2443-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,108 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126384678</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56602</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Klackedammen, Klackedammen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>334151</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6403873</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Varje sommar observeras snok i gödselstacken.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2443-2023 artfynd.xlsx
+++ b/artfynd/A 2443-2023 artfynd.xlsx
@@ -889,6 +889,16 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Emma Westas janco</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emma Westas janco</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 2443-2023 artfynd.xlsx
+++ b/artfynd/A 2443-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>126384678</v>
       </c>
       <c r="B3" t="n">
-        <v>56602</v>
+        <v>56603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2443-2023 artfynd.xlsx
+++ b/artfynd/A 2443-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>126871867</v>
       </c>
       <c r="B4" t="n">
-        <v>56539</v>
+        <v>56543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>126871657</v>
       </c>
       <c r="B5" t="n">
-        <v>58488</v>
+        <v>58492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2443-2023 artfynd.xlsx
+++ b/artfynd/A 2443-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>126871867</v>
       </c>
       <c r="B4" t="n">
-        <v>56543</v>
+        <v>56539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>126871657</v>
       </c>
       <c r="B5" t="n">
-        <v>58492</v>
+        <v>58488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2443-2023 artfynd.xlsx
+++ b/artfynd/A 2443-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139133</v>
+        <v>126384678</v>
       </c>
       <c r="B2" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100088</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lerum, Vg</t>
+          <t>Klackedammen, Klackedammen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333990</v>
+        <v>334151</v>
       </c>
       <c r="R2" t="n">
-        <v>6403735</v>
+        <v>6403873</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,17 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>kläckhål</t>
+          <t>Varje sommar observeras snok i gödselstacken.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Emma Westas janco</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Rostedt</t>
+          <t>Emma Westas janco</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126384678</v>
+        <v>126871867</v>
       </c>
       <c r="B3" t="n">
-        <v>56603</v>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100088</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klackedammen, Klackedammen, Vg</t>
+          <t>Stålebo by, Stålebo, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334151</v>
+        <v>333943</v>
       </c>
       <c r="R3" t="n">
-        <v>6403873</v>
+        <v>6403828</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,34 +852,19 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Varje sommar observeras snok i gödselstacken.</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -891,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emma Westas janco</t>
+          <t>Elisabeth Vansvik</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Westas janco</t>
+          <t>Elisabeth Vansvik</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126871867</v>
+        <v>121139133</v>
       </c>
       <c r="B4" t="n">
-        <v>56543</v>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,34 +895,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stålebo by, Stålebo, Vg</t>
+          <t>Lerum, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333943</v>
+        <v>333990</v>
       </c>
       <c r="R4" t="n">
-        <v>6403828</v>
+        <v>6403735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,19 +958,24 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -988,22 +983,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elisabeth Vansvik</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elisabeth Vansvik</t>
+          <t>Elin Rostedt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126871657</v>
+        <v>121139134</v>
       </c>
       <c r="B5" t="n">
-        <v>58492</v>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,34 +1006,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208245</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stålebo by, Stålebo, Vg</t>
+          <t>Lerum, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>333943</v>
+        <v>333988</v>
       </c>
       <c r="R5" t="n">
-        <v>6403828</v>
+        <v>6403880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,12 +1069,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,15 +1094,112 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Rostedt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126871657</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stålebo by, Stålebo, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>333943</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6403828</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Elisabeth Vansvik</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Elisabeth Vansvik</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2443-2023 artfynd.xlsx
+++ b/artfynd/A 2443-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126871867</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139133</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139134</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126871657</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,8 +1225,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126384678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>